--- a/content/Question Bank/MCQ/Unit 11 - File Handling/Unit 11 - File Handling - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 11 - File Handling/Unit 11 - File Handling - MCQ.xlsx
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why does data stored only in a variable disappear after a Python script finishes running?</t>
+          <t>A student writes a script that calculates their exam average and stores it in a variable, then closes the terminal expecting to see it again tomorrow. Why does data stored only in a variable disappear after a Python script finishes running?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which statement correctly compares a variable's data to a file's data?</t>
+          <t>A librarian's cataloging script keeps a variable in memory alongside a saved records file and needs to check whether the two are in sync. Which statement correctly compares a variable's data to a file's data?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Why is looping directly over an open file object, for line in file:, often preferred over `file.readlines()` for large files?</t>
+          <t>A social media app processes a multi-gigabyte log of user activity and a developer must choose how to read it efficiently. Why is looping directly over an open file object, for line in file:, often preferred over `file.readlines()` for large files?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What happens when `open('missing.txt', 'r')` is called and `missing.txt` does not exist in the script's folder?</t>
+          <t>A backup utility tries to restore a settings file that a user accidentally deleted from the project folder. What happens when `open('missing.txt', 'r')` is called and `missing.txt` does not exist in the script's folder?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What mode does `open('data.txt')` use if no mode argument is given?</t>
+          <t>A note-taking app opens a file to load a user's saved notes without specifying any mode. What mode does `open('data.txt')` use if no mode argument is given?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What is the key difference between `file.read()` and `file.readlines()`?</t>
+          <t>A developer building a chat export tool needs to decide whether to load an entire conversation file at once or split it into separate lines. What is the key difference between `file.read()` and `file.readlines()`?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why should every file opened with `open()` eventually be closed with `.close()`?</t>
+          <t>A developer building an inventory tracker is reviewing why every file the script opens must eventually be released back to the operating system. Why should every file opened with `open()` eventually be closed with `.close()`?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What is the difference between `file.write()` and `file.writelines()`?</t>
+          <t>A quiz app is saving a batch of player names to a results file and the developer isn't sure which method to call. What is the difference between `file.write()` and `file.writelines()`?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which statement about file modes is correct when the target file does not yet exist?</t>
+          <t>A developer is choosing between file modes while designing a system that must run multiple times a day, adding one new line each time without erasing previous entries. Which mode should it use to open the log file?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Why does building a file path with string concatenation, like 'data' + '/' + '`file.txt`', risk breaking on a different operating system?</t>
+          <t>A student setting up a grading script for the first time wonders what actually happens when a file is opened for writing but doesn't already exist on disk. Which statement about file modes is correct when the target file does not yet exist?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What line of code becomes unnecessary once a file is opened using a with block?</t>
+          <t>A developer refactors a report-generation script to use a with block instead of manually managing the file. What line of code becomes unnecessary once a file is opened using a with block?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What is the difference between `Path('.')``.glob('*.txt')` and `Path('.')``.glob('**/*.txt')`?</t>
+          <t>A photo-organizing app needs to decide whether to scan only the top-level folder or every nested subfolder when hunting for image files. What is the difference between `Path('.')``.glob('*.txt')` and `Path('.')``.glob('**/*.txt')`?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which pathlib method lets you write an entire string to a file without a separate `open()` call?</t>
+          <t>A note-taking app wants to save a quick reminder to disk without writing a full open()/write()/close() sequence each time. Which pathlib method lets you write an entire string to a file without a separate `open()` call?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When `csv.reader` reads a row like 'T-shirt,2,350', what type are the individual values in the returned row?</t>
+          <t>A CSV-based product catalog stores rows like `T-shirt,2,350`, and a developer wants to know what type each field arrives as after parsing. When `csv.reader` reads a row like 'T-shirt,2,350', what type are the individual values in the returned row?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What is the difference between `json.dump` and `json.dumps`?</t>
+          <t>A developer building a settings-export feature for a mobile app needs to decide whether to write JSON straight to a file or to a string in memory first. What is the difference between `json.dump` and `json.dumps`?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/content/Question Bank/MCQ/Unit 11 - File Handling/Unit 11 - File Handling - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 11 - File Handling/Unit 11 - File Handling - MCQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Python - MCQ - 11.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Python - MCQ - 11.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python - MCQ - 11.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python - MCQ - 11.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 11.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 11.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 11.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 11.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,14 +643,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Running a single program continuously without ever stopping it</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Storing data only inside a list instead of inside a dictionary</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Running a single program continuously without ever stopping it</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>Making data survive beyond the program run that created it, by saving it to disk</t>
@@ -658,7 +658,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Repeating a loop over and over until some condition becomes false</t>
+          <t>Repeating a loop over and over again until some condition finally becomes false</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -721,26 +721,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>with file = `open('data.txt', 'w')`:</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>with `open('data.txt', 'w')` -&gt; file:</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>with `open('data.txt', 'w')` as file:</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>using `open('data.txt', 'w')` as file:</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>with `open('data.txt', 'w')` -&gt; file:</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>with file = `open('data.txt', 'w')`:</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>with `open('data.txt', 'w')` as file:</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -799,26 +799,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>Any sequence of characters within one folder level</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Exactly one single character only, nothing more</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>Only numeric digits, nothing else at all</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Folders only, but technically never any files</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Any sequence of characters within one folder level</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Exactly one single character only, nothing more</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -884,22 +884,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>['A1\nA2\n']</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>['A1\n', 'A2\n']</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'A1\nA2\n'</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>['A1', 'A2']</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>['A1\n', 'A2\n']</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>['A1\nA2\n']</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>'A1\nA2\n'</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -967,21 +967,21 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>It lets the code check whether the file is present first, avoiding a `FileNotFoundError`</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>It technically and automatically creates the file if it happens to be missing</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>It lets the code check whether the file is present first, avoiding a `FileNotFoundError`</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>It is technically required syntax before every single `open()` call</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1040,26 +1040,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>DictReader lets you access values by column name instead of numeric position, using the header row as keys</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>DictReader technically removes the entire need for an `open()` call altogether every single time it runs</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>DictReader technically and automatically converts all values into integers</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>DictReader is technically faster at reading very large files overall</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>DictReader technically removes the entire need for an `open()` call altogether</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>DictReader lets you access values by column name instead of numeric position, using the header row as keys</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1118,26 +1118,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>CSV technically cannot ever store text values at all, only numbers</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>JSON is technically always considerably smaller in file size than CSV</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>CSV technically handles nested structures far better than JSON ever manages to</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>JSON preserves nested structures, which CSV's flat rows and columns cannot represent at all</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>CSV technically cannot ever store text values at all, only numbers</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>CSV technically handles nested structures far better than JSON ever does</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1196,26 +1196,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>No consequence, both modes behave identically for existing files</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>All previously saved IDs are erased, leaving only the new ID in the file</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>The new ID fails to be written at all</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>No consequence, both modes behave identically for existing files</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Python raises an error before any data is lost</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1280,26 +1280,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>The file is safely closed, containing only 'Line 1', since the crash happens before 'Line 2' is written</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Both lines end up being written completely despite the crash occurring</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>The file is technically left wide open and fully corrupted with absolutely no content at all</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>The file is deleted automatically when an error occurs inside a with block</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Both lines end up being written completely despite the crash occurring</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>The file is safely closed, containing only 'Line 1', since the crash happens before 'Line 2' is written</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>The file is technically left wide open and corrupted with no content at all</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1365,17 +1365,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>Neither check technically matters at all, Python handles both issues completely automatically</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Both lines are technically completely unnecessary boilerplate with absolutely no real functional effect at all here, ever, period</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>`exists()` technically makes the file open faster, and encoding technically only affects file size</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Neither check technically matters at all, Python handles both issues completely automatically</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Both lines are technically completely unnecessary boilerplate with no real functional effect at all</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1549,12 +1549,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>The three lines technically remain completely untouched until something is written</t>
+          <t>The file is immediately and completely erased, losing the three lines, the instant it is opened in 'w' mode</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>The file is immediately and completely erased, losing the three lines, the instant it is opened in 'w' mode</t>
+          <t>The three lines technically remain completely untouched right up until something new is written</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1622,26 +1622,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>Because a variable's lifetime is tied to the running program, and memory clears when it ends</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Because variables are technically always stored on a remote server somewhere</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>Because Python technically deletes all variables automatically every 60 seconds</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Because a variable's lifetime is tied to the running program, and memory clears when it ends</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Because only integer values can technically ever be saved permanently</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Because variables are technically always stored on a remote server somewhere</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1700,26 +1700,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>There is genuinely no real difference at all between the two</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>A variable technically survives the program ending; a file technically does not</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>A file's data persists after the program ends and after a restart; a variable's data does not</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>There is genuinely no real difference at all between the two</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Both survive a program ending, only files survive a restart</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1783,21 +1783,21 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>Write the score to a file so it survives after the program ends</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Store the score inside a global variable at the top level</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>Store it inside a function's own local variable instead</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Store the score inside a global variable at the top level</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Write the score to a file so it survives after the program ends</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>The conversations are technically recreated randomly each time it opens</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>The app technically keeps running invisibly in the background forever</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Variables in Python technically never get cleared at all, ever</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>The conversations are technically recreated randomly each time it opens</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1934,26 +1934,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>It automatically removes all whitespace from each line</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>It technically reads the entire file back in reverse line order instead</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>It is technically the only way Python ever allows reading a file</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>It processes one line at a time, which is far more memory-efficient on large files</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>It automatically removes all whitespace from each line</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>It technically reads the entire file back in reverse order</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>It is technically the only way Python ever allows reading a file</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -2012,26 +2012,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>Python silently returns an empty string</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Python switches to write mode automatically</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Python raises a `FileNotFoundError` immediately</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Python creates an empty file automatically and continues</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Python silently returns an empty string</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Python raises a `FileNotFoundError` immediately</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -2095,21 +2095,21 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>The risk technically only ever applies specifically to files opened in read mode</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>There is genuinely no real risk at all, Python always closes files automatically on any crash whatsoever</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>The file may be left open with incomplete data; with guarantees closure even if an error occurs inside its block</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>The risk technically only ever applies specifically to files opened in read mode</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>There is genuinely no real risk at all, Python always closes files automatically on crash</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -2168,26 +2168,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>'r', read mode</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>'a', append mode</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'x', exclusive creation mode</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>'w', write mode</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>'r', read mode</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>'a', append mode</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>'x', exclusive creation mode</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2246,17 +2246,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>`read()` technically returns a list, `readlines()` technically returns a string</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>`read()` returns one whole string, `readlines()` returns a list of line strings</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>`readlines()` can technically only ever be used once per program</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>`read()` returns one whole string, `readlines()` returns a list of line strings</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>`read()` technically returns a list, `readlines()` technically returns a string</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2425,26 +2425,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>It releases the file back to the operating system and ensures written data is properly saved</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>It technically makes the entire program run measurably faster every single time</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>It is technically only ever required for files opened in read mode</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Python automatically ignores unclosed files with no consequence</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>It is technically only ever required for files opened in read mode</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>It releases the file back to the operating system and ensures written data is properly saved</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>It technically makes the entire program run faster every single time</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2503,22 +2503,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>`writelines()` is technically only ever meant for use with CSV files specifically</t>
+          <t>`writelines()` is technically only ever meant for use with CSV files specifically, nothing else</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>`writelines()` automatically adds a newline after each string, `write()` does not</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>`write()` takes one string, `writelines()` takes a list of strings, and neither adds newlines automatically</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>`write()` can technically only ever be used while in append mode specifically</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>`write()` takes one string, `writelines()` takes a list of strings, and neither adds newlines automatically</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>`writelines()` automatically adds a newline after each string, `write()` does not</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -2585,26 +2585,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>A `SyntaxError`, since two writes cannot be called in a row</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>A101A102, run together on one line</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>A101\nA102\n</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Two separate lines, A101 and A102</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>A101A102, run together on one line</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>A `SyntaxError`, since two writes cannot be called in a row</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2663,26 +2663,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>'w' mode</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>'x' mode, since it is the only safe option</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'r' mode</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>'a' mode</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>'w' mode</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>'r' mode</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2741,14 +2741,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>'r', 'w', and 'a' all create the file automatically if it happens to be missing</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>'w' and 'a' both create a new file if missing; 'r' raises `FileNotFoundError` instead</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>'r', 'w', and 'a' all create the file automatically if missing</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>Only 'w' creates a missing file; 'a' raises an error</t>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2819,26 +2819,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>Different operating systems use different path separator conventions, which a hard-coded slash does not account for</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>String concatenation is technically always noticeably slower than every other available method out there</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>Python technically forbids using the '/' character inside any string at all</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Windows technically does not support the concept of file paths of any kind at all</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>String concatenation is technically always noticeably slower than any other available method</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Different operating systems use different path separator conventions, which a hard-coded slash does not account for</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2897,26 +2897,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>There is genuinely no real difference at all, they are entirely interchangeable in every possible situation</t>
+          <t>There is genuinely no real difference at all, they are entirely interchangeable in every single possible situation here</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>`os.path` technically cannot ever open files at all, only pathlib is truly able to</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>pathlib is technically always faster at reading file contents than any other available method out there</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>pathlib treats paths as objects with built-in cross-platform joining and convenience methods, avoiding fragile manual string handling</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>pathlib is technically always faster at reading file contents than any other available method out there</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>`os.path` technically cannot ever open files at all, only pathlib is truly able to</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2975,26 +2975,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>Hard-coded lists require manual updates whenever files change, unlike a pattern that adapts automatically</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Hard-coded lists are technically always faster, so this is genuinely not risky at all in practice</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Python technically does not allow more than three hard-coded filenames total, ever</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>Glob patterns technically cannot ever be relied upon to match files at all</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Python technically does not allow more than three hard-coded filenames total</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Hard-coded lists require manual updates whenever files change, unlike a pattern that adapts automatically</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Hard-coded lists are technically always faster, so this is genuinely not risky at all</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3053,26 +3053,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>The `open()` call itself</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>The explicit `file.close()` call</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>The mode argument, such as 'r' or 'w'</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>The as keyword</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>The `open()` call itself</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>The explicit `file.close()` call</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>The mode argument, such as 'r' or 'w'</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -3136,26 +3136,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>It raises an error since Path objects cannot use operators</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>It deletes the folder if the file does not exist</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>It joins path pieces together correctly for the current operating system</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>It performs mathematical division between two values</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>It raises an error since Path objects cannot use operators</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>It deletes the folder if the file does not exist</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>It joins path pieces together correctly for the current operating system</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3315,12 +3315,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>No files match since the pattern is invalid</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Only `notes.txt` actually matches here</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No files match since the pattern is invalid</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -3393,26 +3393,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>'**/*.txt' also searches nested subfolders, while '*.txt' only searches the current folder</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>They are technically completely identical to each other in every single case</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'**/*.txt' technically only ever works correctly with CSV files specifically</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>'*.txt' technically searches subfolders, while '**/*.txt' technically does not</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>'**/*.txt' technically only ever works correctly with CSV files specifically</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>'**/*.txt' also searches nested subfolders, while '*.txt' only searches the current folder</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3475,22 +3475,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>It technically converts all numbers into strings completely automatically</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>It prevents extra blank lines from appearing between rows on some operating systems</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>It technically speeds up the writing of large files quite significantly</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>It is required only when using DictWriter, never `csv.writer`</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>It prevents extra blank lines from appearing between rows on some operating systems</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>It technically speeds up the writing of large files quite significantly</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>It technically converts all numbers into strings completely automatically</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -3553,26 +3553,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>`Path.write_text()`</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>`Path.append()`</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>`Path.save()`</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>`Path.write_text()`</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>`Path.dump()`</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>`Path.append()`</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3639,26 +3639,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>The code technically runs correctly and produces the exact right total every single time it runs</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>It raises a `TypeError`, because the values are strings and need `int()` conversion before multiplication</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>It technically and silently produces the value 0 for every single row</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>It technically raises a `FileNotFoundError` instead of anything else</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>It technically and silently produces the value 0 for every single row</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>The code technically runs correctly and produces the exact right total</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>It raises a `TypeError`, because the values are strings and need `int()` conversion before multiplication</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3722,26 +3722,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"coordinates": (15.2993, 74.124)}, tuples are preserved exactly</t>
+          <t>{"coordinates": (15.2993, 74.124)}, tuples are always kept fully intact</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>{"coordinates": "15.2993, 74.124"}, saved as a single string</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>An error is raised, since tuples cannot be serialized at all</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>{"coordinates": [15.2993, 74.124]}, the tuple is silently saved as a JSON array</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>{"coordinates": "15.2993, 74.124"}, saved as a single string</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>An error is raised, since tuples cannot be serialized at all</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3803,22 +3803,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>'reports'</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>'`day1_sales.csv`'</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'day1_sales'</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>'.csv'</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>'reports'</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>'day1_sales'</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>'`day1_sales.csv`'</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>Automatically converted to int or float based on appearance</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Always lists, every single time</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>Always `None`, no matter what</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Always lists, every single time</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Automatically converted to int or float based on appearance</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -3959,26 +3959,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>They are identical, just alternate spellings</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>dump writes directly to an open file; dumps returns a JSON string instead</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>dump only works with lists, dumps only works with dictionaries</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>They are identical, just alternate spellings</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>dumps is only for reading, dump is only for writing</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>dump writes directly to an open file; dumps returns a JSON string instead</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4042,26 +4042,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>It writes the header row using the names in fieldnames, before the data rows are written</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>It technically deletes any existing header row already present in the file</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>It validates that every dictionary in sales has matching keys</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>It technically converts the dictionaries into JSON format before writing them</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>It writes the header row using the names in fieldnames, before the data rows are written</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>It technically deletes any existing header row already present in the file</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>It validates that every dictionary in sales has matching keys</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/content/Question Bank/MCQ/Unit 11 - File Handling/Unit 11 - File Handling - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 11 - File Handling/Unit 11 - File Handling - MCQ.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The with statement syntax is with `open(filename, mode)` as variable_name:, followed by an indented block; this guarantees the file is automatically closed when the block ends.</t>
+          <t>The with statement syntax is with `open(filename, mode)` as `variable_name`:, followed by an indented block; this guarantees the file is automatically closed when the block ends.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -841,7 +841,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>`readlines()` splits the file content at each newline but keeps the newline character attached to each returned line, so the result is ['A1\n', 'A2\n'].</t>
+          <t>`readlines()` splits the file content at each newline but keeps the newline character attached to each returned line, so the result is ['`A1`\n', '`A2`\n'].</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -884,22 +884,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>['A1\nA2\n']</t>
+          <t>['`A1`\nA2\n']</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>['A1\n', 'A2\n']</t>
+          <t>['`A1`\n', '`A2`\n']</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>'A1\nA2\n'</t>
+          <t>'`A1`\nA2\n'</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>['A1', 'A2']</t>
+          <t>['`A1`', '`A2`']</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>A101\nA102\n</t>
+          <t>`A101`\nA102\n</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Two separate lines, A101 and A102</t>
+          <t>Two separate lines, `A101` and `A102`</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A note-taking app wants to save a quick reminder to disk without writing a full open()/write()/close() sequence each time. Which pathlib method lets you write an entire string to a file without a separate `open()` call?</t>
+          <t>A note-taking app wants to save a quick reminder to disk without writing a full `open()`/`write()`/`close()` sequence each time. Which pathlib method lets you write an entire string to a file without a separate `open()` call?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The .stem property returns the filename without its extension, so for '`day1_sales.csv`' it returns 'day1_sales', while .suffix would return just '.csv' and .name would return the full filename.</t>
+          <t>The .stem property returns the filename without its extension, so for '`day1_sales.csv`' it returns '`day1_sales`', while .suffix would return just '.csv' and .name would return the full filename.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>'day1_sales'</t>
+          <t>'`day1_sales`'</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">

--- a/content/Question Bank/MCQ/Unit 11 - File Handling/Unit 11 - File Handling - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 11 - File Handling/Unit 11 - File Handling - MCQ.xlsx
@@ -2693,7 +2693,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A developer is choosing between file modes while designing a system that must run multiple times a day, adding one new line each time without erasing previous entries. Which mode should it use to open the log file?</t>
+          <t>A developer is choosing between file modes and wants to know what happens if the target log file doesn't already exist on disk. Which statement about file modes is correct when the target file does not yet exist?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A student setting up a grading script for the first time wonders what actually happens when a file is opened for writing but doesn't already exist on disk. Which statement about file modes is correct when the target file does not yet exist?</t>
+          <t>A developer hard-codes file paths using a forward slash, like `folder_name + '/' + file_name`, instead of using pathlib. Why can this be risky when the script runs on different operating systems?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>`Path('reports')``.glob('day*_sales.txt')` is used on a folder containing `day1_sales.txt`, `day2_sales.txt`, and `notes.txt`. What gets matched?</t>
+          <t>`Path('reports').glob('day*_sales.txt')` is used on a folder containing `day1_sales.txt`, `day2_sales.txt`, and `notes.txt`. What gets matched?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The pattern day*`_sales.txt` matches any filename starting with 'day', followed by anything, then ending in '`_sales.txt`'; `day1_sales.txt` and `day2_sales.txt` both match, while `notes.txt` does not fit that shape at all.</t>
+          <t>The pattern `day*_sales.txt` matches any filename starting with 'day', followed by anything, then ending in '_sales.txt'; `day1_sales.txt` and `day2_sales.txt` both match, while `notes.txt` does not fit that shape at all.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A photo-organizing app needs to decide whether to scan only the top-level folder or every nested subfolder when hunting for image files. What is the difference between `Path('.')``.glob('*.txt')` and `Path('.')``.glob('**/*.txt')`?</t>
+          <t>A photo-organizing app needs to decide whether to scan only the top-level folder or every nested subfolder when hunting for image files. What is the difference between `Path('.').glob('*.txt')` and `Path('.').glob('**/*.txt')`?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
